--- a/Stock.xlsx
+++ b/Stock.xlsx
@@ -1,2374 +1,2374 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b4d6f46aaed73b6/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{E86B9601-41FB-4938-9621-B839910849E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D96CA58A-50B0-4077-8346-DFE698B034DA}"/>
-  <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="EARRING" sheetId="1" r:id="rId1"/>
-    <sheet name="CHAIN" sheetId="2" r:id="rId2"/>
-    <sheet name="BRACELETS" sheetId="3" r:id="rId3"/>
-    <sheet name="RING" sheetId="4" r:id="rId4"/>
-    <sheet name="LEGWEAR" sheetId="5" r:id="rId5"/>
-    <sheet name="PANDENT" sheetId="6" r:id="rId6"/>
-    <sheet name="Total" sheetId="8" r:id="rId7"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">BRACELETS!$A$1:$R$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CHAIN!$A$1:$R$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EARRING!$A$1:$R$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LEGWEAR!$A$1:$R$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">PANDENT!$A$1:$R$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RING!$A$1:$R$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Total!$A$1:$P$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+  <ns0:fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <ns0:workbookPr defaultThemeVersion="124226"/>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="https://d.docs.live.net/5b4d6f46aaed73b6/Desktop/"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
+  <ns3:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{E86B9601-41FB-4938-9621-B839910849E7}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{D96CA58A-50B0-4077-8346-DFE698B034DA}"/>
+  <ns0:bookViews>
+    <ns0:workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="6" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </ns0:bookViews>
+  <ns0:sheets>
+    <ns0:sheet name="EARRING" sheetId="1" ns7:id="rId1"/>
+    <ns0:sheet name="CHAIN" sheetId="2" ns7:id="rId2"/>
+    <ns0:sheet name="BRACELETS" sheetId="3" ns7:id="rId3"/>
+    <ns0:sheet name="RING" sheetId="4" ns7:id="rId4"/>
+    <ns0:sheet name="LEGWEAR" sheetId="5" ns7:id="rId5"/>
+    <ns0:sheet name="PENDANT" sheetId="6" ns7:id="rId6"/>
+    <ns0:sheet name="Total" sheetId="8" ns7:id="rId7"/>
+  </ns0:sheets>
+  <ns0:definedNames>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">BRACELETS!$A$1:$R$103</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CHAIN!$A$1:$R$89</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EARRING!$A$1:$R$141</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LEGWEAR!$A$1:$R$25</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">PANDENT!$A$1:$R$50</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RING!$A$1:$R$105</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Total!$A$1:$P$1</ns0:definedName>
+  </ns0:definedNames>
+  <ns0:calcPr calcId="191029"/>
+  <ns0:extLst>
+    <ns0:ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns8:calcFeatures>
+        <ns8:feature name="microsoft.com:RD"/>
+        <ns8:feature name="microsoft.com:Single"/>
+        <ns8:feature name="microsoft.com:FV"/>
+        <ns8:feature name="microsoft.com:CNMTM"/>
+        <ns8:feature name="microsoft.com:LET_WF"/>
+        <ns8:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns8:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns8:calcFeatures>
+    </ns0:ext>
+  </ns0:extLst>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7984" uniqueCount="773">
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>subCategory</t>
-  </si>
-  <si>
-    <t>yearOfDesign</t>
-  </si>
-  <si>
-    <t>metalType</t>
-  </si>
-  <si>
-    <t>metalColor</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>quantity</t>
-  </si>
-  <si>
-    <t>madeFor</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>Labour</t>
-  </si>
-  <si>
-    <t>modelImage</t>
-  </si>
-  <si>
-    <t>productImage</t>
-  </si>
-  <si>
-    <t>additional1</t>
-  </si>
-  <si>
-    <t>additional2</t>
-  </si>
-  <si>
-    <t>Earrings</t>
-  </si>
-  <si>
-    <t>Sterling Silver (925)</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>Women</t>
-  </si>
-  <si>
-    <t>Rose</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
-    <t>FASHION</t>
-  </si>
-  <si>
-    <t>DIAEFHW26001</t>
-  </si>
-  <si>
-    <t>NECKLACES</t>
-  </si>
-  <si>
-    <t>DIANFHR26001</t>
-  </si>
-  <si>
-    <t>DIANFHR26002</t>
-  </si>
-  <si>
-    <t>DIANFHR26003</t>
-  </si>
-  <si>
-    <t>DIANFHR26004</t>
-  </si>
-  <si>
-    <t>DIANFHR26005</t>
-  </si>
-  <si>
-    <t>DIANFHW26001</t>
-  </si>
-  <si>
-    <t>17IN</t>
-  </si>
-  <si>
-    <t>18IN</t>
-  </si>
-  <si>
-    <t>DIANFHW26006</t>
-  </si>
-  <si>
-    <t>DIANFHW26005</t>
-  </si>
-  <si>
-    <t>DIANFHW26004</t>
-  </si>
-  <si>
-    <t>DIANFHY26006</t>
-  </si>
-  <si>
-    <t>DIANFHW26007</t>
-  </si>
-  <si>
-    <t>DIANFHW26008</t>
-  </si>
-  <si>
-    <t>DIANFHW26009</t>
-  </si>
-  <si>
-    <t>DIANFHW26010</t>
-  </si>
-  <si>
-    <t>DIANFHW26012</t>
-  </si>
-  <si>
-    <t>DIANFHW26014</t>
-  </si>
-  <si>
-    <t>DIANFHW26015</t>
-  </si>
-  <si>
-    <t>DIANFHW26019</t>
-  </si>
-  <si>
-    <t>DIANFHW26020</t>
-  </si>
-  <si>
-    <t>DIANFHW26021</t>
-  </si>
-  <si>
-    <t>DIANFHW26022</t>
-  </si>
-  <si>
-    <t>DIANFHW26023</t>
-  </si>
-  <si>
-    <t>DIANFHW26024</t>
-  </si>
-  <si>
-    <t>DIANFHW26025</t>
-  </si>
-  <si>
-    <t>DIANFHW26026</t>
-  </si>
-  <si>
-    <t>DIANFHW26029</t>
-  </si>
-  <si>
-    <t>DIANFHR26010</t>
-  </si>
-  <si>
-    <t>DIANFHR26013</t>
-  </si>
-  <si>
-    <t>DIANFHR26014</t>
-  </si>
-  <si>
-    <t>DIANFHY26011</t>
-  </si>
-  <si>
-    <t>DIANFHR26009</t>
-  </si>
-  <si>
-    <t>DIANFHR26015</t>
-  </si>
-  <si>
-    <t>DIANFHR26016</t>
-  </si>
-  <si>
-    <t>DIANFHR26017</t>
-  </si>
-  <si>
-    <t>DIANFHR26018</t>
-  </si>
-  <si>
-    <t>DIANFHR26019</t>
-  </si>
-  <si>
-    <t>DIANFHY26020</t>
-  </si>
-  <si>
-    <t>19IN</t>
-  </si>
-  <si>
-    <t>DIANFHR26027</t>
-  </si>
-  <si>
-    <t>DIANFHR26028</t>
-  </si>
-  <si>
-    <t>BRACELETS</t>
-  </si>
-  <si>
-    <t>DIABFHW26001</t>
-  </si>
-  <si>
-    <t>DIABFHW26002</t>
-  </si>
-  <si>
-    <t>DIABFHW26003</t>
-  </si>
-  <si>
-    <t>DIABFHY26002</t>
-  </si>
-  <si>
-    <t>DIABFHR26002</t>
-  </si>
-  <si>
-    <t>DIABFHR26005</t>
-  </si>
-  <si>
-    <t>DIABFHY26003</t>
-  </si>
-  <si>
-    <t>DIABFHY26004</t>
-  </si>
-  <si>
-    <t>DIABFHW26006</t>
-  </si>
-  <si>
-    <t>DIABFHW26007</t>
-  </si>
-  <si>
-    <t>DIABFHW26008</t>
-  </si>
-  <si>
-    <t>DIABFHR26007</t>
-  </si>
-  <si>
-    <t>DIABFHW26009</t>
-  </si>
-  <si>
-    <t>DIABFHW26012</t>
-  </si>
-  <si>
-    <t>DIABFHR26014</t>
-  </si>
-  <si>
-    <t>DIABFHR26015</t>
-  </si>
-  <si>
-    <t>DIABFHW26016</t>
-  </si>
-  <si>
-    <t>DIABFHW26018</t>
-  </si>
-  <si>
-    <t>DIABFHW26019</t>
-  </si>
-  <si>
-    <t>DIABFHW26020</t>
-  </si>
-  <si>
-    <t>DIABFHW26021</t>
-  </si>
-  <si>
-    <t>DIABFHW26022</t>
-  </si>
-  <si>
-    <t>Men</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>DIABFHW26017</t>
-  </si>
-  <si>
-    <t>TENNIS</t>
-  </si>
-  <si>
-    <t>BOLO</t>
-  </si>
-  <si>
-    <t>2XL</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>4XL</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>DIANFHW26030</t>
-  </si>
-  <si>
-    <t>DIANFHW26031</t>
-  </si>
-  <si>
-    <t>DIARFHW26001</t>
-  </si>
-  <si>
-    <t>RING</t>
-  </si>
-  <si>
-    <t>DIARFHW26003</t>
-  </si>
-  <si>
-    <t>DIARFHW26004</t>
-  </si>
-  <si>
-    <t>DIARFHW26005</t>
-  </si>
-  <si>
-    <t>DIARFHW26006</t>
-  </si>
-  <si>
-    <t>DIARFHW26007</t>
-  </si>
-  <si>
-    <t>DIARFHW26008</t>
-  </si>
-  <si>
-    <t>DIARFHW26009</t>
-  </si>
-  <si>
-    <t>DIARFHW26010</t>
-  </si>
-  <si>
-    <t>DIARFHW26011</t>
-  </si>
-  <si>
-    <t>15,11</t>
-  </si>
-  <si>
-    <t>DIARFHR26002</t>
-  </si>
-  <si>
-    <t>DIARFHW26017</t>
-  </si>
-  <si>
-    <t>DIARFHW26018</t>
-  </si>
-  <si>
-    <t>DIARFHW26020</t>
-  </si>
-  <si>
-    <t>DIARFHW26021</t>
-  </si>
-  <si>
-    <t>DIARFHW26022</t>
-  </si>
-  <si>
-    <t>BAND</t>
-  </si>
-  <si>
-    <t>COCKTAIL</t>
-  </si>
-  <si>
-    <t>DIARBNW26013</t>
-  </si>
-  <si>
-    <t>DIARBNW26014</t>
-  </si>
-  <si>
-    <t>DIARBNW26015</t>
-  </si>
-  <si>
-    <t>11,13</t>
-  </si>
-  <si>
-    <t>DIARBNR26012</t>
-  </si>
-  <si>
-    <t>DIARFHR26017</t>
-  </si>
-  <si>
-    <t>DIARBNR26014</t>
-  </si>
-  <si>
-    <t>DIARFHR26016</t>
-  </si>
-  <si>
-    <t>DIARCTR26019</t>
-  </si>
-  <si>
-    <t>DIARCTW26019</t>
-  </si>
-  <si>
-    <t>DIARFHW26023</t>
-  </si>
-  <si>
-    <t>DIARFHW26024</t>
-  </si>
-  <si>
-    <t>DIARFHR26024</t>
-  </si>
-  <si>
-    <t>DIARFHW26025</t>
-  </si>
-  <si>
-    <t>DIARFHW26026</t>
-  </si>
-  <si>
-    <t>DIARFHR26027</t>
-  </si>
-  <si>
-    <t>DIARFHR26026</t>
-  </si>
-  <si>
-    <t>DIARBNR26028</t>
-  </si>
-  <si>
-    <t>DIARBNW26028</t>
-  </si>
-  <si>
-    <t>DIABFHW26005</t>
-  </si>
-  <si>
-    <t>DIABFHR26006</t>
-  </si>
-  <si>
-    <t>DIABFHY26010</t>
-  </si>
-  <si>
-    <t>DIABFHW26011</t>
-  </si>
-  <si>
-    <t>DIABFHR26013</t>
-  </si>
-  <si>
-    <t>DIABFHW26015</t>
-  </si>
-  <si>
-    <t>DIABFHR26017</t>
-  </si>
-  <si>
-    <t>DIABTNW26023</t>
-  </si>
-  <si>
-    <t>DIABTNR26023</t>
-  </si>
-  <si>
-    <t>DIABBLR26024</t>
-  </si>
-  <si>
-    <t>DIABBLW26024</t>
-  </si>
-  <si>
-    <t>DIABFHW26025</t>
-  </si>
-  <si>
-    <t>DIARFHW26029</t>
-  </si>
-  <si>
-    <t>DIARFHW26031</t>
-  </si>
-  <si>
-    <t>DIARFHW26033</t>
-  </si>
-  <si>
-    <t>DIARFHW26035</t>
-  </si>
-  <si>
-    <t>DIARFHW26037</t>
-  </si>
-  <si>
-    <t>DIARFHR26030</t>
-  </si>
-  <si>
-    <t>DIARFHR26032</t>
-  </si>
-  <si>
-    <t>DIARFHR26034</t>
-  </si>
-  <si>
-    <t>DIARFHR26036</t>
-  </si>
-  <si>
-    <t>DIARFHR26038</t>
-  </si>
-  <si>
-    <t>DIARBNR26039</t>
-  </si>
-  <si>
-    <t>11,14</t>
-  </si>
-  <si>
-    <t>14,11</t>
-  </si>
-  <si>
-    <t>DIARBNR26044</t>
-  </si>
-  <si>
-    <t>DIARBNR26045</t>
-  </si>
-  <si>
-    <t>DIARBNR26047</t>
-  </si>
-  <si>
-    <t>BRIDAL</t>
-  </si>
-  <si>
-    <t>DIARFHR26040</t>
-  </si>
-  <si>
-    <t>DIARFHR26042</t>
-  </si>
-  <si>
-    <t>DIARFHR26043</t>
-  </si>
-  <si>
-    <t>DIARFHW26040</t>
-  </si>
-  <si>
-    <t>DIARFHW26042</t>
-  </si>
-  <si>
-    <t>DIARFHW26043</t>
-  </si>
-  <si>
-    <t>DIARBDR26041</t>
-  </si>
-  <si>
-    <t>DIARBNW26046</t>
-  </si>
-  <si>
-    <t>DIARBNW26047</t>
-  </si>
-  <si>
-    <t>DIARFHW26048</t>
-  </si>
-  <si>
-    <t>DIARFHW26049</t>
-  </si>
-  <si>
-    <t>DIARFHW26050</t>
-  </si>
-  <si>
-    <t>DIARFHW26052</t>
-  </si>
-  <si>
-    <t>DIARFHW26053</t>
-  </si>
-  <si>
-    <t>DIARFHW26054</t>
-  </si>
-  <si>
-    <t>DIARFHW26056</t>
-  </si>
-  <si>
-    <t>DIARFHW26057</t>
-  </si>
-  <si>
-    <t>DIARFHW26058</t>
-  </si>
-  <si>
-    <t>DIARFHW26059</t>
-  </si>
-  <si>
-    <t>DIARFHW26060</t>
-  </si>
-  <si>
-    <t>DIARFHW26061</t>
-  </si>
-  <si>
-    <t>12,14</t>
-  </si>
-  <si>
-    <t>13,16</t>
-  </si>
-  <si>
-    <t>14,12</t>
-  </si>
-  <si>
-    <t>DIARFHR26049</t>
-  </si>
-  <si>
-    <t>DIARFHR26052</t>
-  </si>
-  <si>
-    <t>DIARFHR26053</t>
-  </si>
-  <si>
-    <t>DIARFHR26051</t>
-  </si>
-  <si>
-    <t>DIARFHR26055</t>
-  </si>
-  <si>
-    <t>DIARFHR26056</t>
-  </si>
-  <si>
-    <t>DIARBNR26062</t>
-  </si>
-  <si>
-    <t>DIABFHW26026</t>
-  </si>
-  <si>
-    <t>DIABFHW26027</t>
-  </si>
-  <si>
-    <t>DIABFHW26028</t>
-  </si>
-  <si>
-    <t>DIABFHW26029</t>
-  </si>
-  <si>
-    <t>DIABFHW26030</t>
-  </si>
-  <si>
-    <t>DIABFHW26031</t>
-  </si>
-  <si>
-    <t>DIABFHW26037</t>
-  </si>
-  <si>
-    <t>DIABFHW26038</t>
-  </si>
-  <si>
-    <t>DIABFHR26027</t>
-  </si>
-  <si>
-    <t>DIABFHR26026</t>
-  </si>
-  <si>
-    <t>DIABFHR26030</t>
-  </si>
-  <si>
-    <t>DIABFHR26031</t>
-  </si>
-  <si>
-    <t>DIABBLR26032</t>
-  </si>
-  <si>
-    <t>DIABBLW26032</t>
-  </si>
-  <si>
-    <t>DIABBLW26033</t>
-  </si>
-  <si>
-    <t>DIABBLW26034</t>
-  </si>
-  <si>
-    <t>DIABBLW26035</t>
-  </si>
-  <si>
-    <t>DIABBLW26036</t>
-  </si>
-  <si>
-    <t>DIABBLW26039</t>
-  </si>
-  <si>
-    <t>DIABBLW26040</t>
-  </si>
-  <si>
-    <t>DIABBLR26033</t>
-  </si>
-  <si>
-    <t>DIABBLR26034</t>
-  </si>
-  <si>
-    <t>DIABBLR26035</t>
-  </si>
-  <si>
-    <t>DIABBLR26036</t>
-  </si>
-  <si>
-    <t>DIABFHR26037</t>
-  </si>
-  <si>
-    <t>DIABFHR26038</t>
-  </si>
-  <si>
-    <t>DIABBLW26041</t>
-  </si>
-  <si>
-    <t>DIABFHW26045</t>
-  </si>
-  <si>
-    <t>DIABBLR26039</t>
-  </si>
-  <si>
-    <t>DIABFHW26044</t>
-  </si>
-  <si>
-    <t>DIABTNR26042</t>
-  </si>
-  <si>
-    <t>DIABTNR26043</t>
-  </si>
-  <si>
-    <t>DIABFHW26046</t>
-  </si>
-  <si>
-    <t>DIABFHW26047</t>
-  </si>
-  <si>
-    <t>DIABFHW26048</t>
-  </si>
-  <si>
-    <t>DIABFHW26049</t>
-  </si>
-  <si>
-    <t>DIABFHW26050</t>
-  </si>
-  <si>
-    <t>DIABFHW26051</t>
-  </si>
-  <si>
-    <t>DIABFHW26052</t>
-  </si>
-  <si>
-    <t>DIABFHW26053</t>
-  </si>
-  <si>
-    <t>DIABFHW26055</t>
-  </si>
-  <si>
-    <t>DIABFHW26057</t>
-  </si>
-  <si>
-    <t>DIABFHW26059</t>
-  </si>
-  <si>
-    <t>4XL+</t>
-  </si>
-  <si>
-    <t>DIABFHR26046</t>
-  </si>
-  <si>
-    <t>DIABFHR26047</t>
-  </si>
-  <si>
-    <t>DIABFHR26048</t>
-  </si>
-  <si>
-    <t>DIABFHR26049</t>
-  </si>
-  <si>
-    <t>DIABFHR26050</t>
-  </si>
-  <si>
-    <t>DIABFHR26051</t>
-  </si>
-  <si>
-    <t>DIABFHR26052</t>
-  </si>
-  <si>
-    <t>DIABFHR26053</t>
-  </si>
-  <si>
-    <t>DIABFHR26054</t>
-  </si>
-  <si>
-    <t>DIABFHR26056</t>
-  </si>
-  <si>
-    <t>DIABFHR26058</t>
-  </si>
-  <si>
-    <t>DIABFHR26060</t>
-  </si>
-  <si>
-    <t>DIABFHR26061</t>
-  </si>
-  <si>
-    <t>DIABFHR26062</t>
-  </si>
-  <si>
-    <t>DIABFHR26063</t>
-  </si>
-  <si>
-    <t>DIABFHR26065</t>
-  </si>
-  <si>
-    <t>DIABFHW26065</t>
-  </si>
-  <si>
-    <t>DIABFHW26062</t>
-  </si>
-  <si>
-    <t>DIABFBL26064</t>
-  </si>
-  <si>
-    <t>DIABBLW26064</t>
-  </si>
-  <si>
-    <t>LEGWEAR</t>
-  </si>
-  <si>
-    <t>ANKLET</t>
-  </si>
-  <si>
-    <t>DIALANW26001</t>
-  </si>
-  <si>
-    <t>DIALANW26002</t>
-  </si>
-  <si>
-    <t>DIALANR26001</t>
-  </si>
-  <si>
-    <t>DIALANR26002</t>
-  </si>
-  <si>
-    <t>DIABFHR26066</t>
-  </si>
-  <si>
-    <t>DIALANR26003</t>
-  </si>
-  <si>
-    <t>DIALANW26003</t>
-  </si>
-  <si>
-    <t>DIALANR26004</t>
-  </si>
-  <si>
-    <t>DIALANW26004</t>
-  </si>
-  <si>
-    <t>DIALANR26005</t>
-  </si>
-  <si>
-    <t>DIALANW26005</t>
-  </si>
-  <si>
-    <t>DIALANR26006</t>
-  </si>
-  <si>
-    <t>DIALANW26006</t>
-  </si>
-  <si>
-    <t>DIALANR26007</t>
-  </si>
-  <si>
-    <t>DIALANW26007</t>
-  </si>
-  <si>
-    <t>DIALANR26008</t>
-  </si>
-  <si>
-    <t>DIALANW26008</t>
-  </si>
-  <si>
-    <t>DIALANR26009</t>
-  </si>
-  <si>
-    <t>DIALANW26009</t>
-  </si>
-  <si>
-    <t>DIALANR26010</t>
-  </si>
-  <si>
-    <t>DIALANW26010</t>
-  </si>
-  <si>
-    <t>DIALANW26011</t>
-  </si>
-  <si>
-    <t>DIALANW26012</t>
-  </si>
-  <si>
-    <t>DIALANR26013</t>
-  </si>
-  <si>
-    <t>DIARBNR26063</t>
-  </si>
-  <si>
-    <t>DIARBNR26064</t>
-  </si>
-  <si>
-    <t>DIARBNW26063</t>
-  </si>
-  <si>
-    <t>DIARBNW26064</t>
-  </si>
-  <si>
-    <t>SIGNET</t>
-  </si>
-  <si>
-    <t>YELLOW</t>
-  </si>
-  <si>
-    <t>DIARFHY26065</t>
-  </si>
-  <si>
-    <t>DIARFHR26066</t>
-  </si>
-  <si>
-    <t>DIARBNW26067</t>
-  </si>
-  <si>
-    <t>DIARSNW26068</t>
-  </si>
-  <si>
-    <t>DIARSNW26069</t>
-  </si>
-  <si>
-    <t>DIARBNR26070</t>
-  </si>
-  <si>
-    <t>DIARBNW26070</t>
-  </si>
-  <si>
-    <t>DIARFHR26071</t>
-  </si>
-  <si>
-    <t>DIARFHW26071</t>
-  </si>
-  <si>
-    <t>DIARFHR26072</t>
-  </si>
-  <si>
-    <t>DIARFHW26072</t>
-  </si>
-  <si>
-    <t>DIARFHR26073</t>
-  </si>
-  <si>
-    <t>DIARFHW26073</t>
-  </si>
-  <si>
-    <t>DIARFHR26074</t>
-  </si>
-  <si>
-    <t>DIARFHW26074</t>
-  </si>
-  <si>
-    <t>DIARFHR26075</t>
-  </si>
-  <si>
-    <t>DIARFHW26075</t>
-  </si>
-  <si>
-    <t>DIARFHR26079</t>
-  </si>
-  <si>
-    <t>DIARFHR26080</t>
-  </si>
-  <si>
-    <t>DIARBNW26076</t>
-  </si>
-  <si>
-    <t>DIARBNW26077</t>
-  </si>
-  <si>
-    <t>DIARBNY26078</t>
-  </si>
-  <si>
-    <t>HOOP</t>
-  </si>
-  <si>
-    <t>DIANFHR26032</t>
-  </si>
-  <si>
-    <t>DIANFHR26033</t>
-  </si>
-  <si>
-    <t>DIANFHR26034</t>
-  </si>
-  <si>
-    <t>DIANFHR26035</t>
-  </si>
-  <si>
-    <t>DIANFHW26034</t>
-  </si>
-  <si>
-    <t>DIANFHW26035</t>
-  </si>
-  <si>
-    <t>DIANFHW26036</t>
-  </si>
-  <si>
-    <t>DIANFHR26036</t>
-  </si>
-  <si>
-    <t>DIANFHW26037</t>
-  </si>
-  <si>
-    <t>DIANFHR26037</t>
-  </si>
-  <si>
-    <t>DIANFHW26038</t>
-  </si>
-  <si>
-    <t>DIANFHR26038</t>
-  </si>
-  <si>
-    <t>DIANFHW26039</t>
-  </si>
-  <si>
-    <t>DIANFHR26039</t>
-  </si>
-  <si>
-    <t>DIANFHW26040</t>
-  </si>
-  <si>
-    <t>DIANFHR26040</t>
-  </si>
-  <si>
-    <t>DIANFHW26041</t>
-  </si>
-  <si>
-    <t>16IN</t>
-  </si>
-  <si>
-    <t>DIANFHR26041</t>
-  </si>
-  <si>
-    <t>DIANFHR26042</t>
-  </si>
-  <si>
-    <t>DIANFHR26043</t>
-  </si>
-  <si>
-    <t>DIANFHR26044</t>
-  </si>
-  <si>
-    <t>DIANFHR26045</t>
-  </si>
-  <si>
-    <t>DIANFHW26045</t>
-  </si>
-  <si>
-    <t>DIANFHW26046</t>
-  </si>
-  <si>
-    <t>DIANFHR26046</t>
-  </si>
-  <si>
-    <t>DIANFHW26047</t>
-  </si>
-  <si>
-    <t>DIANFHR26047</t>
-  </si>
-  <si>
-    <t>DIANFHW26048</t>
-  </si>
-  <si>
-    <t>DIANFHR26048</t>
-  </si>
-  <si>
-    <t>DIANFHW26049</t>
-  </si>
-  <si>
-    <t>DIANFHR26049</t>
-  </si>
-  <si>
-    <t>DIANFHW26050</t>
-  </si>
-  <si>
-    <t>DIANFHR26050</t>
-  </si>
-  <si>
-    <t>DIANFHW26051</t>
-  </si>
-  <si>
-    <t>DIANFHR26051</t>
-  </si>
-  <si>
-    <t>DIANFHW26052</t>
-  </si>
-  <si>
-    <t>DIANFHR26052</t>
-  </si>
-  <si>
-    <t>DIANFHW26053</t>
-  </si>
-  <si>
-    <t>DIANFHR26053</t>
-  </si>
-  <si>
-    <t>DIANFHW26054</t>
-  </si>
-  <si>
-    <t>DIANFHW26055</t>
-  </si>
-  <si>
-    <t>DIANFHW26056</t>
-  </si>
-  <si>
-    <t>DIANFHW26057</t>
-  </si>
-  <si>
-    <t>DIANFHR26057</t>
-  </si>
-  <si>
-    <t>DIABFHW26067</t>
-  </si>
-  <si>
-    <t>DIABFHY26068</t>
-  </si>
-  <si>
-    <t>DIARFHR26081</t>
-  </si>
-  <si>
-    <t>STUDS</t>
-  </si>
-  <si>
-    <t>DIANFHW26043</t>
-  </si>
-  <si>
-    <t>DIAEHPW26052</t>
-  </si>
-  <si>
-    <t>DIAEFHW26002</t>
-  </si>
-  <si>
-    <t>DIAEFHR26002</t>
-  </si>
-  <si>
-    <t>DIAEFHW26003</t>
-  </si>
-  <si>
-    <t>DIAEFHR26003</t>
-  </si>
-  <si>
-    <t>DIAEFHR26004</t>
-  </si>
-  <si>
-    <t>DIAEFHW26004</t>
-  </si>
-  <si>
-    <t>DIAEFHR26005</t>
-  </si>
-  <si>
-    <t>DIAEFHW26005</t>
-  </si>
-  <si>
-    <t>DIAEFHY26006</t>
-  </si>
-  <si>
-    <t>DIAEFHR26007</t>
-  </si>
-  <si>
-    <t>DIAEFHR26008</t>
-  </si>
-  <si>
-    <t>DIAEFHR26009</t>
-  </si>
-  <si>
-    <t>DIAEFHW26010</t>
-  </si>
-  <si>
-    <t>DIAEFHR26010</t>
-  </si>
-  <si>
-    <t>DIAEFHR26011</t>
-  </si>
-  <si>
-    <t>DIAEFHR26012</t>
-  </si>
-  <si>
-    <t>DIAEHPW26013</t>
-  </si>
-  <si>
-    <t>DIAEHPR26013</t>
-  </si>
-  <si>
-    <t>DIAEFHW26014</t>
-  </si>
-  <si>
-    <t>DIAEFHR26014</t>
-  </si>
-  <si>
-    <t>DIAEFHW26015</t>
-  </si>
-  <si>
-    <t>DIAEFHR26015</t>
-  </si>
-  <si>
-    <t>DIAEFHW26016</t>
-  </si>
-  <si>
-    <t>DIAEFHR26016</t>
-  </si>
-  <si>
-    <t>DIAEFHW26017</t>
-  </si>
-  <si>
-    <t>DIAEFHR26018</t>
-  </si>
-  <si>
-    <t>DIAEFHY26018</t>
-  </si>
-  <si>
-    <t>DIAEHPW26019</t>
-  </si>
-  <si>
-    <t>DIAEFHW26020</t>
-  </si>
-  <si>
-    <t>DIAEFHW26021</t>
-  </si>
-  <si>
-    <t>DIAEFHR26022</t>
-  </si>
-  <si>
-    <t>DIAEFHR26023</t>
-  </si>
-  <si>
-    <t>DIAEFHR26024</t>
-  </si>
-  <si>
-    <t>DIAEFHR26025</t>
-  </si>
-  <si>
-    <t>DIAESTR26026</t>
-  </si>
-  <si>
-    <t>DIAEFHY26027</t>
-  </si>
-  <si>
-    <t>DIAEFHW26028</t>
-  </si>
-  <si>
-    <t>DIAEFHR26028</t>
-  </si>
-  <si>
-    <t>DIAESTW26029</t>
-  </si>
-  <si>
-    <t>DIAESTR26029</t>
-  </si>
-  <si>
-    <t>DIAEFHW26030</t>
-  </si>
-  <si>
-    <t>DIAEFHR26030</t>
-  </si>
-  <si>
-    <t>DIAEHPW26031</t>
-  </si>
-  <si>
-    <t>DIAEHPR26031</t>
-  </si>
-  <si>
-    <t>DIAESTW26032</t>
-  </si>
-  <si>
-    <t>DIAESTR26032</t>
-  </si>
-  <si>
-    <t>DIAEFHW26033</t>
-  </si>
-  <si>
-    <t>DIAEFHW26034</t>
-  </si>
-  <si>
-    <t>DIAEFHW26035</t>
-  </si>
-  <si>
-    <t>DIAEFHR26035</t>
-  </si>
-  <si>
-    <t>DIAESTW26036</t>
-  </si>
-  <si>
-    <t>DIAESTR26036</t>
-  </si>
-  <si>
-    <t>DIAESTW26037</t>
-  </si>
-  <si>
-    <t>DIAESTR26037</t>
-  </si>
-  <si>
-    <t>DIAESTW26038</t>
-  </si>
-  <si>
-    <t>DIAESTR26038</t>
-  </si>
-  <si>
-    <t>DIAESTW26039</t>
-  </si>
-  <si>
-    <t>DIAEFHW26040</t>
-  </si>
-  <si>
-    <t>DIAEFHR26040</t>
-  </si>
-  <si>
-    <t>DIAESTW26041</t>
-  </si>
-  <si>
-    <t>DIAESTR26041</t>
-  </si>
-  <si>
-    <t>DIAEFHW26042</t>
-  </si>
-  <si>
-    <t>DIAEFHR26042</t>
-  </si>
-  <si>
-    <t>DIAEFHW26043</t>
-  </si>
-  <si>
-    <t>DIAEFHR26043</t>
-  </si>
-  <si>
-    <t>DIAEFHW26044</t>
-  </si>
-  <si>
-    <t>DIAEFHR26045</t>
-  </si>
-  <si>
-    <t>DIAEFHW26046</t>
-  </si>
-  <si>
-    <t>DIAEFHR26047</t>
-  </si>
-  <si>
-    <t>DIAESTW26048</t>
-  </si>
-  <si>
-    <t>DIAEFHR26049</t>
-  </si>
-  <si>
-    <t>DIAEFHW26050</t>
-  </si>
-  <si>
-    <t>DIAEFHW26051</t>
-  </si>
-  <si>
-    <t>DIAEFHW26053</t>
-  </si>
-  <si>
-    <t>DIAEFHR26054</t>
-  </si>
-  <si>
-    <t>DIAEFHR26053</t>
-  </si>
-  <si>
-    <t>DIAESTR26055</t>
-  </si>
-  <si>
-    <t>DIAESTW26055</t>
-  </si>
-  <si>
-    <t>DIAESTR26056</t>
-  </si>
-  <si>
-    <t>DIAESTR26057</t>
-  </si>
-  <si>
-    <t>DIAESTW26057</t>
-  </si>
-  <si>
-    <t>DIAESTW26058</t>
-  </si>
-  <si>
-    <t>DIAEFHW26059</t>
-  </si>
-  <si>
-    <t>DIAEFHR26059</t>
-  </si>
-  <si>
-    <t>DIAEFHW26060</t>
-  </si>
-  <si>
-    <t>DIAEFHR26060</t>
-  </si>
-  <si>
-    <t>DIAESTW26061</t>
-  </si>
-  <si>
-    <t>DIAESTW26063</t>
-  </si>
-  <si>
-    <t>DIAESTW26065</t>
-  </si>
-  <si>
-    <t>DIAESTR26062</t>
-  </si>
-  <si>
-    <t>DIAESTR26064</t>
-  </si>
-  <si>
-    <t>DIAPFHR26001</t>
-  </si>
-  <si>
-    <t>PANDENT</t>
-  </si>
-  <si>
-    <t>DIAPFHR26003</t>
-  </si>
-  <si>
-    <t>DIAPFHW26002</t>
-  </si>
-  <si>
-    <t>DIAPFHW26004</t>
-  </si>
-  <si>
-    <t>DIAPFHW26001</t>
-  </si>
-  <si>
-    <t>DIAPFHR26002</t>
-  </si>
-  <si>
-    <t>DIAPFHW26003</t>
-  </si>
-  <si>
-    <t>DIAPFHR26004</t>
-  </si>
-  <si>
-    <t>DIAESTR26063</t>
-  </si>
-  <si>
-    <t>DIAESTW26062</t>
-  </si>
-  <si>
-    <t>DIAESTW26064</t>
-  </si>
-  <si>
-    <t>DIAESTR26065</t>
-  </si>
-  <si>
-    <t>DIAESTW26066</t>
-  </si>
-  <si>
-    <t>DIAESTR26066</t>
-  </si>
-  <si>
-    <t>DIAESTW26067</t>
-  </si>
-  <si>
-    <t>DIAESTR26067</t>
-  </si>
-  <si>
-    <t>DIAESTW26068</t>
-  </si>
-  <si>
-    <t>DIAESTR26068</t>
-  </si>
-  <si>
-    <t>DIAESTW26069</t>
-  </si>
-  <si>
-    <t>DIAESTR26069</t>
-  </si>
-  <si>
-    <t>DIAESTW26070</t>
-  </si>
-  <si>
-    <t>DIAESTR26070</t>
-  </si>
-  <si>
-    <t>DIAESTW26071</t>
-  </si>
-  <si>
-    <t>DIAESTR26071</t>
-  </si>
-  <si>
-    <t>DIAESTW26072</t>
-  </si>
-  <si>
-    <t>DIAESTR26072</t>
-  </si>
-  <si>
-    <t>DIAESTW26073</t>
-  </si>
-  <si>
-    <t>DIAESTR26073</t>
-  </si>
-  <si>
-    <t>DIAESTW26074</t>
-  </si>
-  <si>
-    <t>DIAESTR26074</t>
-  </si>
-  <si>
-    <t>DIAESTW26075</t>
-  </si>
-  <si>
-    <t>DIAESTR26075</t>
-  </si>
-  <si>
-    <t>DIAESTW26076</t>
-  </si>
-  <si>
-    <t>DIAESTR26076</t>
-  </si>
-  <si>
-    <t>DIAESTW26077</t>
-  </si>
-  <si>
-    <t>DIAESTR26077</t>
-  </si>
-  <si>
-    <t>DIAESTW26078</t>
-  </si>
-  <si>
-    <t>DIAESTR26078</t>
-  </si>
-  <si>
-    <t>DIAESTW26079</t>
-  </si>
-  <si>
-    <t>DIAESTR26079</t>
-  </si>
-  <si>
-    <t>DIAESTW26080</t>
-  </si>
-  <si>
-    <t>DIAESTR26080</t>
-  </si>
-  <si>
-    <t>DIAESTW26082</t>
-  </si>
-  <si>
-    <t>DIAESTW26083</t>
-  </si>
-  <si>
-    <t>DIAESTW26084</t>
-  </si>
-  <si>
-    <t>DIAESTW26085</t>
-  </si>
-  <si>
-    <t>DIAESTW26086</t>
-  </si>
-  <si>
-    <t>DIAESTW26087</t>
-  </si>
-  <si>
-    <t>DIAESTW26088</t>
-  </si>
-  <si>
-    <t>DIAESTW26089</t>
-  </si>
-  <si>
-    <t>DIAESTR26090</t>
-  </si>
-  <si>
-    <t>DIAEFHW26081</t>
-  </si>
-  <si>
-    <t>DIAEFHR26081</t>
-  </si>
-  <si>
-    <t>DIAEFHW26091</t>
-  </si>
-  <si>
-    <t>DIAPFHW26005</t>
-  </si>
-  <si>
-    <t>DIAPFHR26005</t>
-  </si>
-  <si>
-    <t>DIAPFHW26006</t>
-  </si>
-  <si>
-    <t>DIAPFHR26006</t>
-  </si>
-  <si>
-    <t>DIAPFHW26007</t>
-  </si>
-  <si>
-    <t>DIAPFHR26007</t>
-  </si>
-  <si>
-    <t>DIAPFHW26008</t>
-  </si>
-  <si>
-    <t>DIAPFHR26008</t>
-  </si>
-  <si>
-    <t>DIAPFHW26009</t>
-  </si>
-  <si>
-    <t>DIAPFHR26009</t>
-  </si>
-  <si>
-    <t>DIAPFHW26010</t>
-  </si>
-  <si>
-    <t>DIAPFHR26010</t>
-  </si>
-  <si>
-    <t>DIAPFHW26011</t>
-  </si>
-  <si>
-    <t>DIAPFHR26011</t>
-  </si>
-  <si>
-    <t>DIAPFHW26012</t>
-  </si>
-  <si>
-    <t>DIAPFHR26012</t>
-  </si>
-  <si>
-    <t>DIAPFHW26013</t>
-  </si>
-  <si>
-    <t>DIAPFHR26013</t>
-  </si>
-  <si>
-    <t>DIAPFHW26014</t>
-  </si>
-  <si>
-    <t>DIAPFHR26014</t>
-  </si>
-  <si>
-    <t>DIAPFHW26015</t>
-  </si>
-  <si>
-    <t>DIAPFHR26015</t>
-  </si>
-  <si>
-    <t>DIAPFHW26016</t>
-  </si>
-  <si>
-    <t>DIAPFHR26016</t>
-  </si>
-  <si>
-    <t>DIAPFHW26017</t>
-  </si>
-  <si>
-    <t>DIAPFHR26017</t>
-  </si>
-  <si>
-    <t>DIAPFHW26018</t>
-  </si>
-  <si>
-    <t>DIAPFHR26018</t>
-  </si>
-  <si>
-    <t>DIAPFHW26019</t>
-  </si>
-  <si>
-    <t>DIAPFHR26019</t>
-  </si>
-  <si>
-    <t>DIAPFHW26020</t>
-  </si>
-  <si>
-    <t>DIAPFHR26021</t>
-  </si>
-  <si>
-    <t>DIAPFHW26022</t>
-  </si>
-  <si>
-    <t>DIAPFHR26023</t>
-  </si>
-  <si>
-    <t>DIAPFHW26024</t>
-  </si>
-  <si>
-    <t>DIAPFHR26025</t>
-  </si>
-  <si>
-    <t>DIAPFHW26026</t>
-  </si>
-  <si>
-    <t>DIAPFHR26027</t>
-  </si>
-  <si>
-    <t>DIAPFHW26028</t>
-  </si>
-  <si>
-    <t>DIAPFHR26029</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>Product Source</t>
-  </si>
-  <si>
-    <t>Procured</t>
-  </si>
-  <si>
-    <t>chain</t>
-  </si>
-  <si>
-    <t>bracelet</t>
-  </si>
-  <si>
-    <t>ring</t>
-  </si>
-  <si>
-    <t>legwear</t>
-  </si>
-  <si>
-    <t>pendent</t>
-  </si>
-  <si>
-    <t>rate</t>
-  </si>
-  <si>
-    <t>sold</t>
-  </si>
-  <si>
-    <t>cash1800</t>
-  </si>
-  <si>
-    <t>cash 1200</t>
-  </si>
-  <si>
-    <t>upi 1224</t>
-  </si>
-  <si>
-    <t>upi 2956</t>
-  </si>
-  <si>
-    <t>6300 upi</t>
-  </si>
-  <si>
-    <t>2400 upi</t>
-  </si>
-  <si>
-    <t>2300 upi</t>
-  </si>
-  <si>
-    <t>E19602</t>
-  </si>
-  <si>
-    <t>E19758</t>
-  </si>
-  <si>
-    <t>E19762</t>
-  </si>
-  <si>
-    <t>E19785</t>
-  </si>
-  <si>
-    <t>E19796</t>
-  </si>
-  <si>
-    <t>E19810</t>
-  </si>
-  <si>
-    <t>E19813</t>
-  </si>
-  <si>
-    <t>E19836</t>
-  </si>
-  <si>
-    <t>E19838</t>
-  </si>
-  <si>
-    <t>E19839</t>
-  </si>
-  <si>
-    <t>E19852</t>
-  </si>
-  <si>
-    <t>E19856</t>
-  </si>
-  <si>
-    <t>E19861</t>
-  </si>
-  <si>
-    <t>E19863</t>
-  </si>
-  <si>
-    <t>E19881</t>
-  </si>
-  <si>
-    <t>E19886</t>
-  </si>
-  <si>
-    <t>E19932</t>
-  </si>
-  <si>
-    <t>E19969</t>
-  </si>
-  <si>
-    <t>E19982</t>
-  </si>
-  <si>
-    <t>E20155</t>
-  </si>
-  <si>
-    <t>E20179</t>
-  </si>
-  <si>
-    <t>E20336</t>
-  </si>
-  <si>
-    <t>E20410</t>
-  </si>
-  <si>
-    <t>E20575</t>
-  </si>
-  <si>
-    <t>E20580</t>
-  </si>
-  <si>
-    <t>E20610</t>
-  </si>
-  <si>
-    <t>E20771</t>
-  </si>
-  <si>
-    <t>E20955</t>
-  </si>
-  <si>
-    <t>E21116</t>
-  </si>
-  <si>
-    <t>E21203</t>
-  </si>
-  <si>
-    <t>E21220</t>
-  </si>
-  <si>
-    <t>E21287</t>
-  </si>
-  <si>
-    <t>E21348</t>
-  </si>
-  <si>
-    <t>N00147</t>
-  </si>
-  <si>
-    <t>P00942</t>
-  </si>
-  <si>
-    <t>P01036</t>
-  </si>
-  <si>
-    <t>P01375</t>
-  </si>
-  <si>
-    <t>P01384</t>
-  </si>
-  <si>
-    <t>P01419</t>
-  </si>
-  <si>
-    <t>P01481</t>
-  </si>
-  <si>
-    <t>P01537</t>
-  </si>
-  <si>
-    <t>P01549</t>
-  </si>
-  <si>
-    <t>P01628</t>
-  </si>
-  <si>
-    <t>P01703</t>
-  </si>
-  <si>
-    <t>P01728</t>
-  </si>
-  <si>
-    <t>P01746</t>
-  </si>
-  <si>
-    <t>P01767</t>
-  </si>
-  <si>
-    <t>P01793</t>
-  </si>
-  <si>
-    <t>P01889</t>
-  </si>
-  <si>
-    <t>P01967</t>
-  </si>
-  <si>
-    <t>P02047</t>
-  </si>
-  <si>
-    <t>P02151</t>
-  </si>
-  <si>
-    <t>P02233</t>
-  </si>
-  <si>
-    <t>P02242</t>
-  </si>
-  <si>
-    <t>P02317</t>
-  </si>
-  <si>
-    <t>P02327</t>
-  </si>
-  <si>
-    <t>P02337</t>
-  </si>
-  <si>
-    <t>P02357</t>
-  </si>
-  <si>
-    <t>P02374</t>
-  </si>
-  <si>
-    <t>P02393</t>
-  </si>
-  <si>
-    <t>P02463</t>
-  </si>
-  <si>
-    <t>P02546</t>
-  </si>
-  <si>
-    <t>P02796</t>
-  </si>
-  <si>
-    <t>P02867</t>
-  </si>
-  <si>
-    <t>P02889</t>
-  </si>
-  <si>
-    <t>P02895</t>
-  </si>
-  <si>
-    <t>P02940</t>
-  </si>
-  <si>
-    <t>P03051</t>
-  </si>
-  <si>
-    <t>P03135</t>
-  </si>
-  <si>
-    <t>P03161</t>
-  </si>
-  <si>
-    <t>P03550</t>
-  </si>
-  <si>
-    <t>P03696</t>
-  </si>
-  <si>
-    <t>P03718</t>
-  </si>
-  <si>
-    <t>P03863</t>
-  </si>
-  <si>
-    <t>P03912</t>
-  </si>
-  <si>
-    <t>P03940</t>
-  </si>
-  <si>
-    <t>P03944</t>
-  </si>
-  <si>
-    <t>P03969</t>
-  </si>
-  <si>
-    <t>P04478</t>
-  </si>
-  <si>
-    <t>VMR0810</t>
-  </si>
-  <si>
-    <t>PKR0850</t>
-  </si>
-  <si>
-    <t>R00722</t>
-  </si>
-  <si>
-    <t>R01594</t>
-  </si>
-  <si>
-    <t>R02060</t>
-  </si>
-  <si>
-    <t>R02416</t>
-  </si>
-  <si>
-    <t>R03421</t>
-  </si>
-  <si>
-    <t>R03469</t>
-  </si>
-  <si>
-    <t>R03502</t>
-  </si>
-  <si>
-    <t>R03540</t>
-  </si>
-  <si>
-    <t>R03551</t>
-  </si>
-  <si>
-    <t>R03564</t>
-  </si>
-  <si>
-    <t>B02845</t>
-  </si>
-  <si>
-    <t>B03070</t>
-  </si>
-  <si>
-    <t>B03126</t>
-  </si>
-  <si>
-    <t>B03385</t>
-  </si>
-  <si>
-    <t>B03389</t>
-  </si>
-  <si>
-    <t>B03392</t>
-  </si>
-  <si>
-    <t>B03401</t>
-  </si>
-  <si>
-    <t>B03417</t>
-  </si>
-  <si>
-    <t>B03481</t>
-  </si>
-  <si>
-    <t>B03534</t>
-  </si>
-  <si>
-    <t>B04005</t>
-  </si>
-  <si>
-    <t>B04038</t>
-  </si>
-  <si>
-    <t>B04043</t>
-  </si>
-  <si>
-    <t>B04082</t>
-  </si>
-  <si>
-    <t>E07462</t>
-  </si>
-  <si>
-    <t>E09130</t>
-  </si>
-  <si>
-    <t>E09191</t>
-  </si>
-  <si>
-    <t>E09289</t>
-  </si>
-  <si>
-    <t>E10453</t>
-  </si>
-  <si>
-    <t>E10552</t>
-  </si>
-  <si>
-    <t>E10938</t>
-  </si>
-  <si>
-    <t>E11789</t>
-  </si>
-  <si>
-    <t>E11805</t>
-  </si>
-  <si>
-    <t>E14213</t>
-  </si>
-  <si>
-    <t>E14257</t>
-  </si>
-  <si>
-    <t>E14276</t>
-  </si>
-  <si>
-    <t>E14537</t>
-  </si>
-  <si>
-    <t>E15170</t>
-  </si>
-  <si>
-    <t>E15582</t>
-  </si>
-  <si>
-    <t>E15830</t>
-  </si>
-  <si>
-    <t>E16099</t>
-  </si>
-  <si>
-    <t>E16318</t>
-  </si>
-  <si>
-    <t>E16370</t>
-  </si>
-  <si>
-    <t>E16392</t>
-  </si>
-  <si>
-    <t>E16503</t>
-  </si>
-  <si>
-    <t>E16804</t>
-  </si>
-  <si>
-    <t>E16821</t>
-  </si>
-  <si>
-    <t>E16826</t>
-  </si>
-  <si>
-    <t>E16830</t>
-  </si>
-  <si>
-    <t>E16913</t>
-  </si>
-  <si>
-    <t>E16971</t>
-  </si>
-  <si>
-    <t>E16972</t>
-  </si>
-  <si>
-    <t>E16976</t>
-  </si>
-  <si>
-    <t>E17009</t>
-  </si>
-  <si>
-    <t>E17023</t>
-  </si>
-  <si>
-    <t>E17031</t>
-  </si>
-  <si>
-    <t>E17037</t>
-  </si>
-  <si>
-    <t>E17039</t>
-  </si>
-  <si>
-    <t>E17046</t>
-  </si>
-  <si>
-    <t>E17047</t>
-  </si>
-  <si>
-    <t>E17092</t>
-  </si>
-  <si>
-    <t>E17414</t>
-  </si>
-  <si>
-    <t>E17627</t>
-  </si>
-  <si>
-    <t>E18595</t>
-  </si>
-  <si>
-    <t>E19001</t>
-  </si>
-  <si>
-    <t>E19017</t>
-  </si>
-  <si>
-    <t>E19032</t>
-  </si>
-  <si>
-    <t>E19043</t>
-  </si>
-  <si>
-    <t>E19053</t>
-  </si>
-  <si>
-    <t>E19059</t>
-  </si>
-  <si>
-    <t>E19062</t>
-  </si>
-  <si>
-    <t>E19079</t>
-  </si>
-  <si>
-    <t>E19085</t>
-  </si>
-  <si>
-    <t>E19091</t>
-  </si>
-  <si>
-    <t>E19111</t>
-  </si>
-  <si>
-    <t>E19130</t>
-  </si>
-  <si>
-    <t>E19138</t>
-  </si>
-  <si>
-    <t>E19166</t>
-  </si>
-  <si>
-    <t>E19173</t>
-  </si>
-  <si>
-    <t>E19189</t>
-  </si>
-  <si>
-    <t>E19193</t>
-  </si>
-  <si>
-    <t>E19197</t>
-  </si>
-  <si>
-    <t>E19207</t>
-  </si>
-  <si>
-    <t>E19239</t>
-  </si>
-  <si>
-    <t>E19254</t>
-  </si>
-  <si>
-    <t>E19259</t>
-  </si>
-  <si>
-    <t>E19329</t>
-  </si>
-  <si>
-    <t>E19408</t>
-  </si>
-  <si>
-    <t>E19435</t>
-  </si>
-  <si>
-    <t>E19590</t>
-  </si>
-  <si>
-    <t>SOLD</t>
-  </si>
-  <si>
-    <t>2500 CASH</t>
-  </si>
-  <si>
-    <t>3350 UPI</t>
-  </si>
-  <si>
-    <t>1675 UPI</t>
-  </si>
-  <si>
-    <t>DIAEFHW26058</t>
-  </si>
-  <si>
-    <t>1336UPI</t>
-  </si>
-  <si>
-    <t>1700 CASH</t>
-  </si>
-  <si>
-    <t>UPI 5887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2431 upi </t>
-  </si>
-  <si>
-    <t>upi 1496</t>
-  </si>
-  <si>
-    <t>upi 10349</t>
-  </si>
-  <si>
-    <t>upi 1355</t>
-  </si>
-  <si>
-    <t>upi 2590</t>
-  </si>
-  <si>
-    <t>upi 2032</t>
-  </si>
-  <si>
-    <t>upi 1981</t>
-  </si>
-  <si>
-    <t>1900 upi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sold </t>
-  </si>
-  <si>
-    <t>3500 upi</t>
-  </si>
-  <si>
-    <t>old</t>
-  </si>
-  <si>
-    <t>7474 upi</t>
-  </si>
-  <si>
-    <t>3300 cash</t>
-  </si>
-  <si>
-    <t>5900 cash</t>
-  </si>
-  <si>
-    <t>2700 cash</t>
-  </si>
-  <si>
-    <t>10500 cash</t>
-  </si>
-  <si>
-    <t>2500 cash</t>
-  </si>
-  <si>
-    <t>2450 uoi</t>
-  </si>
-  <si>
-    <t>3200 upi</t>
-  </si>
-</sst>
+<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7984" uniqueCount="773">
+  <ns0:si>
+    <ns0:t>title</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>price</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SKU</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>category</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>subCategory</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>yearOfDesign</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>metalType</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>metalColor</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>size</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>quantity</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>madeFor</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>weight</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Labour</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>modelImage</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>productImage</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>additional1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>additional2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Earrings</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sterling Silver (925)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>White</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Women</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Rose</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Yellow</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>FASHION</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NECKLACES</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17IN</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>18IN</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHY26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26020</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26021</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26022</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26023</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26024</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26025</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26029</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHY26011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26016</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26018</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHY26020</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>19IN</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26028</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BRACELETS</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHY26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHY26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHY26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26016</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26018</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26020</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26021</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26022</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Men</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>A</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TENNIS</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BOLO</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2XL</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>XL</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4XL</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>M</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>L</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26030</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>RING</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>15,11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26018</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26020</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26021</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26022</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BAND</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>COCKTAIL</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11,13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26016</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARCTR26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARCTW26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26023</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26024</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26024</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26025</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26028</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26028</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHY26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABTNW26023</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABTNR26023</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLR26024</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26024</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26025</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26029</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26033</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26030</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26034</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26039</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11,14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14,11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26044</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26045</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BRIDAL</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26040</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26042</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26040</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26042</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBDR26041</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26048</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26049</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26050</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26052</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26054</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26056</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26057</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26058</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26059</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26060</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26061</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12,14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13,16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14,12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26049</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26052</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26051</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26055</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26056</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26062</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26028</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26029</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26030</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26030</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLR26032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26033</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26034</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26039</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26040</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLR26033</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLR26034</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLR26035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLR26036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26041</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26045</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLR26039</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26044</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABTNR26042</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABTNR26043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26048</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26049</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26050</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26051</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26052</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26055</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26057</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26059</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4XL+</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26048</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26049</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26050</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26051</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26052</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26054</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26056</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26058</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26060</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26061</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26062</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26063</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26065</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26065</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26062</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFBL26064</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABBLW26064</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LEGWEAR</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ANKLET</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHR26066</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANW26012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIALANR26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26063</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26064</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26063</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26064</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SIGNET</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>YELLOW</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHY26065</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26066</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26067</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARSNW26068</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARSNW26069</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNR26070</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26070</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26071</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26071</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26072</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26072</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26073</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26073</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26074</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26074</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26075</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHW26075</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26079</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26080</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26076</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNW26077</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARBNY26078</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>HOOP</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26033</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26034</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26034</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26039</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26039</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26040</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26040</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26041</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>16IN</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26041</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26042</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26044</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26045</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26045</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26048</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26048</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26049</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26049</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26050</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26050</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26051</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26051</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26052</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26052</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26054</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26055</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26056</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26057</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHR26057</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHW26067</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIABFHY26068</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIARFHR26081</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>STUDS</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIANFHW26043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEHPW26052</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHY26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEHPW26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEHPR26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26016</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26016</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26018</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHY26018</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEHPW26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26020</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26021</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26022</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26023</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26024</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26025</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHY26027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26028</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26028</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26029</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26029</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26030</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26030</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEHPW26031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEHPR26031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26033</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26034</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26035</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26039</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26040</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26040</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26041</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26041</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26042</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26042</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26044</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26045</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26048</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26049</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26050</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26051</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26054</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26055</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26055</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26056</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26057</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26057</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26058</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26059</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26059</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26060</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26060</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26061</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26063</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26065</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26062</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26064</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>PENDANT</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26002</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26003</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26004</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26063</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26062</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26064</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26065</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26066</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26066</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26067</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26067</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26068</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26068</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26069</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26069</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26070</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26070</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26071</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26071</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26072</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26072</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26073</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26073</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26074</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26074</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26075</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26075</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26076</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26076</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26077</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26077</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26078</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26078</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26079</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26079</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26080</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26080</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26082</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26083</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26084</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26085</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26086</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26087</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26088</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTW26089</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAESTR26090</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26081</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHR26081</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26091</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26006</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26007</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26008</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26010</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26013</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26014</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26016</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26016</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26018</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26018</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26020</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26021</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26022</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26023</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26024</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26025</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26026</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHW26028</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAPFHR26029</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MEN</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Product Source</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Procured</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>chain</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>bracelet</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ring</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>legwear</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>pendent</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>rate</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>sold</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>cash1800</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>cash 1200</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 1224</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 2956</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6300 upi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2400 upi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2300 upi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19602</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19758</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19762</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19785</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19796</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19810</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19813</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19836</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19838</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19839</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19852</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19856</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19861</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19863</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19881</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19886</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19932</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19969</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19982</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20155</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20179</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20336</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20410</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20575</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20580</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20610</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20771</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E20955</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E21116</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E21203</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E21220</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E21287</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E21348</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>N00147</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P00942</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01375</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01384</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01419</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01481</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01537</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01549</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01628</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01703</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01728</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01746</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01767</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01793</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01889</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P01967</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02151</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02233</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02242</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02317</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02327</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02337</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02357</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02374</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02393</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02463</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02546</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02796</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02867</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02889</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02895</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P02940</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03051</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03135</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03161</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03550</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03696</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03718</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03863</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03912</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03940</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03944</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P03969</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>P04478</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>VMR0810</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>PKR0850</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R00722</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R01594</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R02060</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R02416</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R03421</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R03469</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R03502</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R03540</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R03551</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>R03564</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B02845</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03070</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03126</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03385</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03389</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03392</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03401</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03417</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03481</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B03534</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B04005</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B04038</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B04043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>B04082</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E07462</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E09130</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E09191</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E09289</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E10453</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E10552</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E10938</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E11789</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E11805</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E14213</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E14257</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E14276</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E14537</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E15170</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E15582</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E15830</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16099</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16318</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16370</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16392</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16503</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16804</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16821</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16826</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16830</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16913</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16971</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16972</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E16976</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17009</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17023</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17037</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17039</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17047</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17092</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17414</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E17627</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E18595</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19001</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19053</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19059</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19062</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19079</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19085</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19091</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19111</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19130</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19138</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19166</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19173</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19189</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19193</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19197</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19207</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19239</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19254</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19259</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19329</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19408</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19435</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>E19590</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SOLD</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2500 CASH</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3350 UPI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1675 UPI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DIAEFHW26058</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1336UPI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1700 CASH</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>UPI 5887</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t xml:space="preserve">2431 upi </ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 1496</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 10349</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 1355</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 2590</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 2032</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upi 1981</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1900 upi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t xml:space="preserve">sold </ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3500 upi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>old</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7474 upi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3300 cash</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5900 cash</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2700 cash</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10500 cash</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2500 cash</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2450 uoi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3200 upi</ns0:t>
+  </ns0:si>
+</ns0:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
